--- a/DacTa.xlsx
+++ b/DacTa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5F01B4-2219-4608-AAD4-E7507387049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F793DB-72D7-474A-AC6B-F30CB2E1EAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2D3A772F-016C-49AF-AEE7-0A1E08B82DE4}"/>
   </bookViews>
@@ -89,12 +89,6 @@
     <t>Đặc tả use case</t>
   </si>
   <si>
-    <t>quản lý tài khoản và phân quyền</t>
-  </si>
-  <si>
-    <t>người dùng bấm vào quản lý tài khoản và phân quyền</t>
-  </si>
-  <si>
     <t>Hệ thống hỗ trợ admin quản lý tài khoản của nhân viên trong doanh nghiệp</t>
   </si>
   <si>
@@ -107,9 +101,6 @@
   </si>
   <si>
     <t>Lỗi hệ thống hoặc database</t>
-  </si>
-  <si>
-    <t>Username không trùng, password được mã hóa</t>
   </si>
   <si>
     <t>1. Admin truy cập chức năng “Quản lý tài khoản”
@@ -137,20 +128,11 @@
     <t>người dùng đã đăng nhập thành công</t>
   </si>
   <si>
-    <t>người dùng bấm vào tạo tài khoản tại quản lý tài khoản và phân quyền</t>
-  </si>
-  <si>
     <t>1.Hệ thống đã đăng nhập thành công và role phải là Admin
 2.Hệ thống đang ở form quản lý tài khoản và phân quyền</t>
   </si>
   <si>
     <t>Hệ thống hỗ trợ admin thêm tài khoản vào cơ sở dữ liệu</t>
-  </si>
-  <si>
-    <t>tạo tài khoản</t>
-  </si>
-  <si>
-    <t>tài khoản mới được thêm vào hệ thống</t>
   </si>
   <si>
     <t>3A. Thông tin đầu vào chứa các ký tự không hợp lệ, hệ thống yêu cầu nhập lại
@@ -174,9 +156,6 @@
   </si>
   <si>
     <t>Hiện ra tài khoản của nhân viên dựa trên EmployeeId</t>
-  </si>
-  <si>
-    <t>Tìm kiếm tài khoản</t>
   </si>
   <si>
     <t>1. Admin chọn “Tìm kiếm”
@@ -227,9 +206,6 @@
     <t>Dữ liệu tồn tại trong hệ thống</t>
   </si>
   <si>
-    <t>Xóa tài khoản</t>
-  </si>
-  <si>
     <t>người dùng bấm vào xóa tài khoản tại quản lý tài khoản và phân quyền</t>
   </si>
   <si>
@@ -237,6 +213,41 @@
   </si>
   <si>
     <t>Tài khoản của nhân viên bị xóa khỏi cơ sở dữ liệu</t>
+  </si>
+  <si>
+    <t>1. Admin chọn “Xóa tài khoản”
+2. Hệ thống hiển thị form
+3. Admin nhập:EmployeeId
+4.Xác nhận
+5.Xóa tài khoản khỏi cơ sở dữ liệu và cập nhật trạng thái isActive của nhân viên thành false</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Có thể thêm soft delete</t>
+  </si>
+  <si>
+    <t>Không vi phạm ràng buộc các khóa</t>
+  </si>
+  <si>
+    <t>3A. Hệ thống không tìm thấy EmployeeId tương ứng trong cơ sở dữ liệu và thông báo không tìm thấy
+4A.Admin bấm hủy thì hoàn tác</t>
+  </si>
+  <si>
+    <t>Admin bấm vào quản lý tài khoản và phân quyền</t>
+  </si>
+  <si>
+    <t>UC_04 Quản lý tài khoản và phân quyền</t>
+  </si>
+  <si>
+    <t>UC04_01 tạo tài khoản</t>
+  </si>
+  <si>
+    <t>Người dùng bấm vào tạo tài khoản tại quản lý tài khoản và phân quyền</t>
+  </si>
+  <si>
+    <t>Tài khoản mới được thêm vào hệ thống</t>
   </si>
   <si>
     <t>1. Admin chọn “Tạo tài khoản”
@@ -245,29 +256,18 @@
    - username
    - password
    - role
-   - EmployeeId
+   - mã nhân viên
 4. Hệ thống xác thực
-5. Lưu DB và cập nhật status isActive của nhân viên thành true</t>
-  </si>
-  <si>
-    <t>1. Admin chọn “Xóa tài khoản”
-2. Hệ thống hiển thị form
-3. Admin nhập:EmployeeId
-4.Xác nhận
-5.Xóa tài khoản khỏi cơ sở dữ liệu và cập nhật trạng thái isActive của nhân viên thành false</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Có thể thêm soft delete</t>
-  </si>
-  <si>
-    <t>Không vi phạm ràng buộc các khóa</t>
-  </si>
-  <si>
-    <t>3A. Hệ thống không tìm thấy EmployeeId tương ứng trong cơ sở dữ liệu và thông báo không tìm thấy
-4A.Admin bấm hủy thì hoàn tác</t>
+5. Lưu DB và cập nhật statuss của nhân viên thành true</t>
+  </si>
+  <si>
+    <t>password được mã hóa</t>
+  </si>
+  <si>
+    <t>UC04_2 Tìm kiếm tài khoản</t>
+  </si>
+  <si>
+    <t>UC04_3Xóa tài khoản</t>
   </si>
 </sst>
 </file>
@@ -371,10 +371,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -392,15 +401,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -744,166 +744,166 @@
   <cols>
     <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>46026</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46026</v>
-      </c>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="3:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+    </row>
+    <row r="12" spans="3:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="3:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" spans="3:6" ht="129.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="3:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="E13" s="12"/>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" spans="3:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="3:6" ht="151.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="3:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="14"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="14"/>
+      <c r="D17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="14"/>
+      <c r="D18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="14"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="14"/>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.3">
       <c r="D21" s="1"/>
@@ -912,6 +912,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
@@ -920,14 +928,6 @@
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -943,167 +943,173 @@
   <sheetData>
     <row r="7" spans="4:7" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="4:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="4:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="3" t="s">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="4:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6"/>
+      <c r="E9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="4:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="10">
         <v>46026</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="12"/>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="13"/>
+    </row>
+    <row r="14" spans="4:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="4:7" ht="144.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" spans="4:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="4:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10"/>
-    </row>
-    <row r="15" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10"/>
-    </row>
-    <row r="16" spans="4:7" ht="144.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="4:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="14"/>
+      <c r="E20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="14"/>
+      <c r="E21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="14"/>
+      <c r="E22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14"/>
+      <c r="E23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="E12:G12"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="E22:G22"/>
@@ -1114,12 +1120,6 @@
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="E13:G13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1131,171 +1131,177 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="9" width="23" customWidth="1"/>
-    <col min="10" max="10" width="36.44140625" customWidth="1"/>
+    <col min="10" max="10" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="9" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="6"/>
+      <c r="H10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="G11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="10">
         <v>46026</v>
       </c>
-      <c r="J11" s="6"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="G12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="6"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
+      <c r="H13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
     </row>
     <row r="14" spans="7:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
+      <c r="H14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
     </row>
     <row r="15" spans="7:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
+      <c r="H15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
     </row>
     <row r="16" spans="7:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
+      <c r="H16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
     </row>
     <row r="17" spans="7:10" ht="115.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
+      <c r="H17" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="7:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
+      <c r="H18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="14"/>
+      <c r="H19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="5"/>
     </row>
     <row r="20" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
     </row>
     <row r="21" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="14"/>
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="5"/>
     </row>
     <row r="22" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="13"/>
-      <c r="J22" s="14"/>
+      <c r="H22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="5"/>
     </row>
     <row r="23" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="14"/>
+      <c r="H23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="5"/>
     </row>
     <row r="24" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="14"/>
+      <c r="H24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="H13:J13"/>
     <mergeCell ref="H21:J21"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H23:J23"/>
@@ -1306,12 +1312,6 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="H20:J20"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1323,166 +1323,166 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="9" max="11" width="23" customWidth="1"/>
-    <col min="12" max="12" width="36.44140625" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="10" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
     </row>
     <row r="11" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
+        <v>46026</v>
+      </c>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="13"/>
+    </row>
+    <row r="15" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+    </row>
+    <row r="16" spans="9:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="13"/>
+    </row>
+    <row r="17" spans="9:12" x14ac:dyDescent="0.3">
+      <c r="I17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="L17" s="13"/>
+    </row>
+    <row r="18" spans="9:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="13"/>
+    </row>
+    <row r="19" spans="9:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7">
-        <v>46026</v>
-      </c>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="9:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="9:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="9:12" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="10"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="13"/>
     </row>
     <row r="20" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J20" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="K20" s="13"/>
-      <c r="L20" s="14"/>
+      <c r="J20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
     </row>
     <row r="21" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
     </row>
     <row r="22" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J22" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K22" s="13"/>
-      <c r="L22" s="14"/>
+      <c r="J22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="5"/>
     </row>
     <row r="23" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="14"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="5"/>
     </row>
     <row r="24" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J24" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="K24" s="13"/>
-      <c r="L24" s="14"/>
+      <c r="J24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="5"/>
     </row>
     <row r="25" spans="9:12" x14ac:dyDescent="0.3">
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J25" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="K25" s="13"/>
-      <c r="L25" s="14"/>
+      <c r="J25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="16">
